--- a/output/pdf_financials_xlsx/CCMC.xlsx
+++ b/output/pdf_financials_xlsx/CCMC.xlsx
@@ -4796,43 +4796,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.1032</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1032</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.255403</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.243123</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.235239</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.224116</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.231961</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.104966</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.433474</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.522916</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.019077</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.61721</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.600747</v>
       </c>
     </row>
     <row r="93">
@@ -5953,16 +5953,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.015439</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.092011</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -7656,7 +7656,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -8147,7 +8151,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9047,7 +9055,11 @@
           <t>Reserves 7,9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9430,7 +9442,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -10038,7 +10054,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -10676,7 +10696,11 @@
           <t>Share based payment reserve 7</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.1032</v>
       </c>
@@ -14980,7 +15004,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>-0.015439</v>
       </c>

--- a/output/pdf_financials_xlsx/CCMC.xlsx
+++ b/output/pdf_financials_xlsx/CCMC.xlsx
@@ -833,22 +833,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.002693</v>
+        <v>0.013263</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.054889</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.061485</v>
+        <v>0.25355</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.052851</v>
+        <v>0.08390599999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.059682</v>
+        <v>0.08422399999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.06951300000000001</v>
+        <v>0.106732</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.080068</v>
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.0054</v>
+        <v>-0.054889</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.061485</v>
+        <v>-0.25355</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.052851</v>
+        <v>-0.08390599999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.059682</v>
+        <v>-0.08422399999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.06951300000000001</v>
+        <v>-0.106732</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.080068</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003413</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009829999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.919087</v>
+        <v>-0.9225</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.269525</v>
+        <v>-0.270508</v>
       </c>
     </row>
     <row r="28">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.919087</v>
+        <v>-0.9225</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.269525</v>
+        <v>-0.270508</v>
       </c>
     </row>
     <row r="30">
@@ -2052,34 +2052,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002638</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007997000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.274079</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.14449</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.091596</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.028526</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.031448</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000452</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.638176</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.124572</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.995097</v>
@@ -2144,34 +2144,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002638</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007997000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.274079</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.14449</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.091596</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.028526</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.031448</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000452</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.638176</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.124572</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>1.053097</v>
@@ -2696,34 +2696,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.005123</v>
+        <v>0.002485</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.009933000000000001</v>
+        <v>0.001936</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.285429</v>
+        <v>0.01135</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.150825</v>
+        <v>0.006335</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.098166</v>
+        <v>0.00657</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.029696</v>
+        <v>0.00117</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.037408</v>
+        <v>0.00596</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.008451999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.727838</v>
+        <v>0.08966200000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.175358</v>
+        <v>0.050786</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -23207,10 +23207,10 @@
         </is>
       </c>
       <c r="I208" s="5" t="n">
-        <v>-0.08422399999999999</v>
+        <v>0.08422399999999999</v>
       </c>
       <c r="J208" s="5" t="n">
-        <v>-0.106732</v>
+        <v>0.106732</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -23991,23 +23991,23 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>-0.013263</v>
+        <v>0.013263</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>-0.054889</v>
+        <v>0.054889</v>
       </c>
       <c r="G218" s="5" t="n">
-        <v>-0.25355</v>
+        <v>0.25355</v>
       </c>
       <c r="H218" s="5" t="n">
-        <v>-0.08390599999999999</v>
+        <v>0.08390599999999999</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>-0.08422399999999999</v>
+        <v>0.08422399999999999</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CCMC.xlsx
+++ b/output/pdf_financials_xlsx/CCMC.xlsx
@@ -1174,7 +1174,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.008907999999999999</v>
+        <v>-0.008907999999999999</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1362,10 +1362,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.000857</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.047434</v>
@@ -3611,40 +3609,40 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.01146</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.027363</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.064364</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.025999</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="68">
@@ -16232,7 +16230,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -16396,7 +16398,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>0.000857</v>
       </c>
@@ -16558,7 +16564,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -25123,7 +25133,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -25536,7 +25550,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
